--- a/extenbooks/S1001_extenbook.xlsx
+++ b/extenbooks/S1001_extenbook.xlsx
@@ -1780,7 +1780,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2888,11 +2888,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2915,88 +2915,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bank vs Private Industry IROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ingested</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1001_research.json", "adequacy_report": "Technical/docs/chapters/CH10_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1001_DPR.md", "epr": "Technical/docs/series/S1001_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1001_load.py", "processor": "Technical/code/P02_processors/P02_S1001_construct.py", "validator": "Technical/code/V03_validators/V03_S1001_validate.py", "processed": "Technical/data/processed/S1001.parquet", "chopped_csv": "Technical/chopped/S1001.csv", "extenbook_xlsx": "Technical/extenbooks/S1001_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S1001-A", "S1001-B"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_APP72_ALLPRIV", "SHAIKH_APP72_BANKS"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1001_extenbook.xlsx
+++ b/extenbooks/S1001_extenbook.xlsx
@@ -1794,7 +1794,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-fanout-ch10</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chapter 10 ("Modern Money and Inflation") opens by arguing that financial-sector profit rates do *not* diverge systematically from industrial profit rates — banking competes for capital like any other industry. Figure 10.1 is the empirical anchor: bank IROP fluctuates around the all-private IROP. Shaikh references Appendix 7.2 (Ch7 industry-level S215 IROP panel) for the underlying derivation.</t>
+          <t>Chapter 10 ("Competition, Finance, and Interest Rates") opens by arguing that financial-sector profit rates do *not* diverge systematically from industrial profit rates — banking competes for capital like any other industry. Figure 10.1 is the empirical anchor: bank IROP fluctuates around the all-private IROP. Shaikh references Appendix 7.2 (Ch7 industry-level S215 IROP panel) for the underlying derivation.</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:26:02.539593+00:00</t>
+          <t>2026-07-02T06:18:07.676950+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1001_extenbook.xlsx
+++ b/extenbooks/S1001_extenbook.xlsx
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:07.676950+00:00</t>
+          <t>2026-07-11T03:44:22.074331+00:00</t>
         </is>
       </c>
     </row>
@@ -2888,11 +2888,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2915,6 +2915,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP72_BANKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Figure 10.1 (bank vs all-private IROP, 1988-2005) faithfully from Shaikh Appendix 7.2; pass-through, KB-verified caption. Fixed hallucinated chapter title and spurious Fig10.2 reference.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1001_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1001_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rate_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
